--- a/uniqorn-frontend/public/data/CurrentSeason_UniqornGames_Master.xlsx
+++ b/uniqorn-frontend/public/data/CurrentSeason_UniqornGames_Master.xlsx
@@ -486,42 +486,42 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jaden</t>
+          <t>Alperen</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>McDaniels</t>
+          <t>Sengun</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -570,12 +570,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rudy</t>
+          <t>Jaden</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gobert</t>
+          <t>McDaniels</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -610,38 +610,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Rudy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Gobert</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="n">
         <v>19</v>
       </c>
-      <c r="G5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
       <c r="I5" t="n">
         <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -650,118 +650,118 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Scottie</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Barnes</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>Scottie</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wembanyama</t>
+          <t>Barnes</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H7" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46075</v>
+        <v>46076</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ingram</t>
+          <t>Wembanyama</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>17</v>
+      </c>
+      <c r="I8" t="n">
         <v>6</v>
       </c>
-      <c r="H8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -770,38 +770,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Horford</t>
+          <t>Ingram</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>22</v>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -810,32 +810,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nikola</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jokic</t>
+          <t>Horford</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>GSW</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>DEN</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>GSW</t>
-        </is>
-      </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="G10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
@@ -846,42 +846,42 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46074</v>
+        <v>46075</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cade</t>
+          <t>Nikola</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cunningham</t>
+          <t>Jokic</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
         <v>3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -890,38 +890,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tyrese</t>
+          <t>Matas</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Maxey</t>
+          <t>Buzelis</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -930,78 +930,78 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Matas</t>
+          <t>Tyrese</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Buzelis</t>
+          <t>Maxey</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" t="n">
         <v>3</v>
       </c>
-      <c r="H13" t="n">
-        <v>6</v>
-      </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kam</t>
+          <t>Cade</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Cunningham</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1086,42 +1086,42 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cade</t>
+          <t>Kam</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cunningham</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1130,38 +1130,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jaylen</t>
+          <t>Precious</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Achiuwa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="G18" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Derrick</t>
+          <t>Jaylen</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1189,19 +1189,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="G19" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1210,78 +1210,78 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Precious</t>
+          <t>Derrick</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Achiuwa</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46065</v>
+        <v>46072</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bobby</t>
+          <t>Cade</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portis</t>
+          <t>Cunningham</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H21" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1290,78 +1290,78 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Donovan</t>
+          <t>Bobby</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Clingan</t>
+          <t>Portis</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G22" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jalen</t>
+          <t>Donovan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Suggs</t>
+          <t>Clingan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I23" t="n">
         <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1406,79 +1406,79 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Josh</t>
+          <t>Jalen</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hart</t>
+          <t>Suggs</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H25" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Donovan</t>
+          <t>Josh</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mitchell</t>
+          <t>Hart</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>2</v>
@@ -1490,38 +1490,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Maxime</t>
+          <t>Jalen</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raynaud</t>
+          <t>Suggs</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H27" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -1530,75 +1530,75 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jalen</t>
+          <t>Maxime</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Suggs</t>
+          <t>Raynaud</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="G28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Scottie</t>
+          <t>Donovan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Barnes</t>
+          <t>Mitchell</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H29" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>2</v>
@@ -1610,78 +1610,78 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kawhi</t>
+          <t>Scottie</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Leonard</t>
+          <t>Barnes</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H30" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Alperen</t>
+          <t>Kawhi</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sengun</t>
+          <t>Leonard</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="G31" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -1690,38 +1690,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Jusuf</t>
+          <t>Jahmai</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nurkic</t>
+          <t>Mashack</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
         <v>6</v>
-      </c>
-      <c r="H32" t="n">
-        <v>14</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1730,35 +1730,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nikola</t>
+          <t>Jusuf</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jokic</t>
+          <t>Nurkic</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="G33" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H33" t="n">
         <v>14</v>
       </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -1770,38 +1770,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jalen</t>
+          <t>Alperen</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Suggs</t>
+          <t>Sengun</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="F34" t="n">
+        <v>17</v>
+      </c>
+      <c r="G34" t="n">
+        <v>11</v>
+      </c>
+      <c r="H34" t="n">
         <v>12</v>
       </c>
-      <c r="G34" t="n">
-        <v>6</v>
-      </c>
-      <c r="H34" t="n">
-        <v>7</v>
-      </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -1810,72 +1810,72 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jahmai</t>
+          <t>Jalen</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mashack</t>
+          <t>Suggs</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Derrick</t>
+          <t>Nikola</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Jokic</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G36" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I36" t="n">
         <v>4</v>
@@ -1886,42 +1886,42 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Jalen</t>
+          <t>Derrick</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Suggs</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G37" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H37" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I37" t="n">
         <v>4</v>
       </c>
       <c r="J37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1930,38 +1930,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Jalen</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Durant</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G38" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -1970,38 +1970,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Jalen</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Durant</t>
+          <t>Suggs</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H39" t="n">
+        <v>11</v>
+      </c>
+      <c r="I39" t="n">
+        <v>4</v>
+      </c>
+      <c r="J39" t="n">
         <v>3</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -2010,38 +2010,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Jalen</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kalkbrenner</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H40" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I40" t="n">
         <v>2</v>
       </c>
       <c r="J40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2086,42 +2086,42 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Jalen</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brunson</t>
+          <t>Kalkbrenner</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="G42" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -2170,35 +2170,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Neemias</t>
+          <t>Jalen</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Queta</t>
+          <t>Brunson</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H44" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>2</v>
@@ -2210,78 +2210,78 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Neemias</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Porter Jr.</t>
+          <t>Queta</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G45" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J45" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Filipowski</t>
+          <t>Porter Jr.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G46" t="n">
+        <v>9</v>
+      </c>
+      <c r="H46" t="n">
+        <v>6</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
         <v>5</v>
-      </c>
-      <c r="H46" t="n">
-        <v>16</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -2290,38 +2290,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Matas</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Buzelis</t>
+          <t>Filipowski</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I47" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -2330,35 +2330,35 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Jamal</t>
+          <t>Matas</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>Buzelis</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="G48" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2406,82 +2406,82 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dominick</t>
+          <t>Jamal</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Barlow</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H50" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cade</t>
+          <t>Dominick</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cunningham</t>
+          <t>Barlow</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G51" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H51" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -2530,38 +2530,38 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Donovan</t>
+          <t>Jarrett</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Clingan</t>
+          <t>Allen</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>Cavaliers</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>Trail Blazers</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Cavaliers</t>
-        </is>
-      </c>
       <c r="F53" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="G53" t="n">
         <v>5</v>
       </c>
       <c r="H53" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I53" t="n">
         <v>4</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -2610,78 +2610,78 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Jarrett</t>
+          <t>Donovan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Allen</t>
+          <t>Clingan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>Trail Blazers</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>Cavaliers</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Trail Blazers</t>
-        </is>
-      </c>
       <c r="F55" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="G55" t="n">
         <v>5</v>
       </c>
       <c r="H55" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I55" t="n">
         <v>4</v>
       </c>
       <c r="J55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rudy</t>
+          <t>Cade</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Gobert</t>
+          <t>Cunningham</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H56" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -2690,78 +2690,78 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Yves</t>
+          <t>Rudy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Missi</t>
+          <t>Gobert</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I57" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ausar</t>
+          <t>Yves</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Thompson</t>
+          <t>Missi</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>7</v>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H58" t="n">
         <v>8</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J58" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -2770,35 +2770,35 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jaren</t>
+          <t>Ausar</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jackson Jr.</t>
+          <t>Thompson</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G59" t="n">
         <v>2</v>
       </c>
       <c r="H59" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
         <v>6</v>
@@ -2810,118 +2810,118 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Derrick</t>
+          <t>Jaren</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Jackson Jr.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G60" t="n">
+        <v>2</v>
+      </c>
+      <c r="H60" t="n">
         <v>9</v>
       </c>
-      <c r="H60" t="n">
-        <v>2</v>
-      </c>
       <c r="I60" t="n">
         <v>2</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Myles</t>
+          <t>Derrick</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H61" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I61" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>Myles</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wembanyama</t>
+          <t>Turner</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -2930,38 +2930,38 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Draymond</t>
+          <t>Karl-Anthony</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Towns</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G63" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -2970,38 +2970,38 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Wembanyama</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G64" t="n">
+        <v>3</v>
+      </c>
+      <c r="H64" t="n">
+        <v>16</v>
+      </c>
+      <c r="I64" t="n">
         <v>5</v>
       </c>
-      <c r="H64" t="n">
-        <v>7</v>
-      </c>
-      <c r="I64" t="n">
-        <v>2</v>
-      </c>
       <c r="J64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -3010,38 +3010,38 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Dyson</t>
+          <t>Draymond</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Daniels</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H65" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -3050,38 +3050,38 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Collin</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Murray-Boyles</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="G66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H66" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -3090,38 +3090,38 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>OG</t>
+          <t>Dyson</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Anunoby</t>
+          <t>Daniels</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="G67" t="n">
+        <v>9</v>
+      </c>
+      <c r="H67" t="n">
+        <v>6</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" t="n">
         <v>5</v>
-      </c>
-      <c r="H67" t="n">
-        <v>3</v>
-      </c>
-      <c r="I67" t="n">
-        <v>2</v>
-      </c>
-      <c r="J67" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="68">
@@ -3130,35 +3130,35 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Karl-Anthony</t>
+          <t>Collin</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Towns</t>
+          <t>Murray-Boyles</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>Raptors</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>Knicks</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Raptors</t>
-        </is>
-      </c>
       <c r="F68" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H68" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3166,42 +3166,42 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>OG</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Harden</t>
+          <t>Anunoby</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H69" t="n">
         <v>3</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
@@ -3210,78 +3210,78 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>James</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sarr</t>
+          <t>Harden</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G70" t="n">
+        <v>10</v>
+      </c>
+      <c r="H70" t="n">
         <v>3</v>
       </c>
-      <c r="H70" t="n">
-        <v>12</v>
-      </c>
       <c r="I70" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cam</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Sarr</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="G71" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H71" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -3326,39 +3326,39 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Scottie</t>
+          <t>Cam</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Barnes</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G73" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H73" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>1</v>
@@ -3406,42 +3406,42 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46045</v>
+        <v>46047</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Donovan</t>
+          <t>Scottie</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Clingan</t>
+          <t>Barnes</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H75" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -3450,78 +3450,78 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Scottie</t>
+          <t>Donovan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Barnes</t>
+          <t>Clingan</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t>Trail Blazers</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>Raptors</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Trail Blazers</t>
-        </is>
-      </c>
       <c r="F76" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G76" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H76" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I76" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Jake</t>
+          <t>Scottie</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LaRavia</t>
+          <t>Barnes</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H77" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I77" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -3530,78 +3530,78 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Peyton</t>
+          <t>Jake</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Watson</t>
+          <t>LaRavia</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="G78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" t="n">
+        <v>5</v>
+      </c>
+      <c r="I78" t="n">
+        <v>4</v>
+      </c>
+      <c r="J78" t="n">
         <v>3</v>
-      </c>
-      <c r="H78" t="n">
-        <v>8</v>
-      </c>
-      <c r="I78" t="n">
-        <v>4</v>
-      </c>
-      <c r="J78" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Peyton</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cardwell</t>
+          <t>Watson</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="G79" t="n">
         <v>3</v>
       </c>
       <c r="H79" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I79" t="n">
         <v>4</v>
       </c>
       <c r="J79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -3646,82 +3646,82 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Alperen</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sengun</t>
+          <t>Cardwell</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G81" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H81" t="n">
         <v>13</v>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cade</t>
+          <t>Alperen</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cunningham</t>
+          <t>Sengun</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G82" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H82" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I82" t="n">
         <v>2</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -3730,38 +3730,38 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tyrese</t>
+          <t>Cade</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Maxey</t>
+          <t>Cunningham</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G83" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J83" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -3770,78 +3770,78 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Jalen</t>
+          <t>Tyrese</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Maxey</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G84" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H84" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I84" t="n">
         <v>1</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46039</v>
+        <v>46041</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Jamal</t>
+          <t>Jalen</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G85" t="n">
         <v>6</v>
       </c>
       <c r="H85" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -3850,78 +3850,78 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Jamal</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Edwards</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="G86" t="n">
+        <v>6</v>
+      </c>
+      <c r="H86" t="n">
         <v>3</v>
       </c>
-      <c r="H86" t="n">
-        <v>4</v>
-      </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46038</v>
+        <v>46039</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Miller</t>
+          <t>Edwards</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="G87" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -3930,78 +3930,78 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tyrese</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Maxey</t>
+          <t>Miller</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G88" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H88" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Oso</t>
+          <t>Tyrese</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ighodaro</t>
+          <t>Maxey</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H89" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J89" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
@@ -4010,75 +4010,75 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Jaren</t>
+          <t>Oso</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Jackson Jr.</t>
+          <t>Ighodaro</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
         <v>3</v>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Scottie</t>
+          <t>Jaren</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Barnes</t>
+          <t>Jackson Jr.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G91" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J91" t="n">
         <v>2</v>
@@ -4086,42 +4086,42 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Shai</t>
+          <t>Scottie</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Gilgeous-Alexander</t>
+          <t>Barnes</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G92" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H92" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I92" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -4166,82 +4166,82 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>46033</v>
+        <v>46035</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Goga</t>
+          <t>Shai</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bitadze</t>
+          <t>Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H94" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J94" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Kawhi</t>
+          <t>Goga</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Leonard</t>
+          <t>Bitadze</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G95" t="n">
         <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Kris</t>
+          <t>Kawhi</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Dunn</t>
+          <t>Leonard</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4269,13 +4269,13 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="G96" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
@@ -4286,42 +4286,42 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Stephen</t>
+          <t>Kris</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Curry</t>
+          <t>Dunn</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="G97" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98">
@@ -4330,78 +4330,78 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Derik</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Queen</t>
+          <t>Curry</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G98" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H98" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
         <v>2</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Mouhamed</t>
+          <t>Derik</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Gueye</t>
+          <t>Queen</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G99" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H99" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I99" t="n">
         <v>2</v>
       </c>
       <c r="J99" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -4410,35 +4410,35 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Steven</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Adams</t>
+          <t>Wembanyama</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G100" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H100" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I100" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J100" t="n">
         <v>2</v>
@@ -4450,38 +4450,38 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>Mouhamed</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wembanyama</t>
+          <t>Gueye</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G101" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H101" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I101" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102">
@@ -4526,39 +4526,39 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Luka</t>
+          <t>Steven</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Doncic</t>
+          <t>Adams</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G103" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H103" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J103" t="n">
         <v>2</v>
@@ -4570,35 +4570,35 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Craig</t>
+          <t>Luka</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Porter Jr.</t>
+          <t>Doncic</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="G104" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H104" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>2</v>
@@ -4606,42 +4606,42 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Tyrese</t>
+          <t>Craig</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Maxey</t>
+          <t>Porter Jr.</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="G105" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H105" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J105" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -4650,75 +4650,75 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cade</t>
+          <t>Tyrese</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Cunningham</t>
+          <t>Maxey</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G106" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H106" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I106" t="n">
         <v>2</v>
       </c>
       <c r="J106" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Cade</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Cunningham</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G107" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H107" t="n">
         <v>3</v>
       </c>
       <c r="I107" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
         <v>1</v>
@@ -4766,42 +4766,42 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Kornet</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G109" t="n">
+        <v>10</v>
+      </c>
+      <c r="H109" t="n">
         <v>3</v>
       </c>
-      <c r="H109" t="n">
-        <v>8</v>
-      </c>
       <c r="I109" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -4810,38 +4810,38 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Sandro</t>
+          <t>Dyson</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Mamukelashvili</t>
+          <t>Daniels</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
+          <t>Hawks</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
           <t>Raptors</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Hawks</t>
-        </is>
-      </c>
       <c r="F110" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G110" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H110" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -4850,38 +4850,38 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Dyson</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Daniels</t>
+          <t>Kornet</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G111" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H111" t="n">
+        <v>8</v>
+      </c>
+      <c r="I111" t="n">
         <v>5</v>
       </c>
-      <c r="I111" t="n">
-        <v>2</v>
-      </c>
       <c r="J111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -4926,21 +4926,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ariel</t>
+          <t>Sandro</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hukporti</t>
+          <t>Mamukelashvili</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4949,16 +4949,16 @@
         </is>
       </c>
       <c r="F113" t="n">
+        <v>13</v>
+      </c>
+      <c r="G113" t="n">
         <v>8</v>
       </c>
-      <c r="G113" t="n">
-        <v>4</v>
-      </c>
       <c r="H113" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I113" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J113" t="n">
         <v>1</v>
@@ -4966,42 +4966,42 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Kawhi</t>
+          <t>Ariel</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Leonard</t>
+          <t>Hukporti</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="G114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H114" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I114" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -5010,32 +5010,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Kel'el</t>
+          <t>Kawhi</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ware</t>
+          <t>Leonard</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H115" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I115" t="n">
         <v>2</v>
@@ -5046,39 +5046,39 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>46022</v>
+        <v>46023</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Chet</t>
+          <t>Kel'el</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Holmgren</t>
+          <t>Ware</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I116" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J116" t="n">
         <v>2</v>
@@ -5086,42 +5086,42 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Derrick</t>
+          <t>Chet</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Holmgren</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>10</v>
+      </c>
+      <c r="I117" t="n">
         <v>6</v>
       </c>
-      <c r="H117" t="n">
-        <v>7</v>
-      </c>
-      <c r="I117" t="n">
-        <v>7</v>
-      </c>
       <c r="J117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
@@ -5130,35 +5130,35 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Cedric</t>
+          <t>Derrick</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Coward</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G118" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H118" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -5166,42 +5166,42 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>46019</v>
+        <v>46021</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Tyrese</t>
+          <t>Cedric</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Maxey</t>
+          <t>Coward</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
+          <t>Grizzlies</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
           <t>76ers</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Thunder</t>
         </is>
       </c>
       <c r="F119" t="n">
         <v>28</v>
       </c>
       <c r="G119" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H119" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -5210,38 +5210,38 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Kawhi</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Leonard</t>
+          <t>Sarr</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="G120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I120" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J120" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -5250,38 +5250,38 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Kawhi</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Sarr</t>
+          <t>Leonard</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H121" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I121" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J121" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122">
@@ -5290,38 +5290,38 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Chet</t>
+          <t>Tyrese</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Holmgren</t>
+          <t>Maxey</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
+          <t>76ers</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
           <t>Thunder</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>76ers</t>
-        </is>
-      </c>
       <c r="F122" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G122" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H122" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I122" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123">
@@ -5330,78 +5330,78 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Scottie</t>
+          <t>Chet</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Barnes</t>
+          <t>Holmgren</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G123" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H123" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46018</v>
+        <v>46019</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>Scottie</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Wembanyama</t>
+          <t>Barnes</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G124" t="n">
+        <v>10</v>
+      </c>
+      <c r="H124" t="n">
+        <v>25</v>
+      </c>
+      <c r="I124" t="n">
+        <v>1</v>
+      </c>
+      <c r="J124" t="n">
         <v>3</v>
-      </c>
-      <c r="H124" t="n">
-        <v>7</v>
-      </c>
-      <c r="I124" t="n">
-        <v>5</v>
-      </c>
-      <c r="J124" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -5450,38 +5450,38 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Yves</t>
+          <t>Nikola</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Missi</t>
+          <t>Jokic</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="G126" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H126" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="I126" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -5490,57 +5490,57 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Nikola</t>
+          <t>Yves</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Jokic</t>
+          <t>Missi</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="G127" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H127" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46017</v>
+        <v>46018</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Cade</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Cunningham</t>
+          <t>Wembanyama</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5549,19 +5549,19 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G128" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H128" t="n">
+        <v>7</v>
+      </c>
+      <c r="I128" t="n">
         <v>5</v>
       </c>
-      <c r="I128" t="n">
-        <v>2</v>
-      </c>
       <c r="J128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -5650,38 +5650,38 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Trae</t>
+          <t>Desmond</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Young</t>
+          <t>Bane</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G131" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H131" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -5690,32 +5690,32 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Cade</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Cunningham</t>
+          <t>Harper</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G132" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H132" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I132" t="n">
         <v>0</v>
@@ -5730,38 +5730,38 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Nikola</t>
+          <t>Trae</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Jokic</t>
+          <t>Young</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G133" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H133" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I133" t="n">
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -5770,38 +5770,38 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Nikola</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Harper</t>
+          <t>Jokic</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="G134" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H134" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I134" t="n">
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135">
@@ -5810,38 +5810,38 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Desmond</t>
+          <t>Cade</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bane</t>
+          <t>Cunningham</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F135" t="n">
         <v>23</v>
       </c>
       <c r="G135" t="n">
+        <v>14</v>
+      </c>
+      <c r="H135" t="n">
+        <v>7</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
         <v>5</v>
-      </c>
-      <c r="H135" t="n">
-        <v>4</v>
-      </c>
-      <c r="I135" t="n">
-        <v>3</v>
-      </c>
-      <c r="J135" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -5850,38 +5850,38 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Isaiah</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Davis</t>
+          <t>Collier</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="G136" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H136" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
@@ -5890,38 +5890,38 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Moussa</t>
+          <t>Nikola</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Diabate</t>
+          <t>Jokic</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G137" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H137" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I137" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J137" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
@@ -5930,38 +5930,38 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Isaiah</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Collier</t>
+          <t>Davis</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="G138" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H138" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -5970,38 +5970,38 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Nikola</t>
+          <t>Moussa</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Jokic</t>
+          <t>Diabate</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F139" t="n">
+        <v>5</v>
+      </c>
+      <c r="G139" t="n">
+        <v>2</v>
+      </c>
+      <c r="H139" t="n">
         <v>14</v>
       </c>
-      <c r="G139" t="n">
-        <v>13</v>
-      </c>
-      <c r="H139" t="n">
-        <v>13</v>
-      </c>
       <c r="I139" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140">
@@ -6010,38 +6010,38 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Kel'el</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ware</t>
+          <t>Porter Jr.</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H140" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141">
@@ -6050,38 +6050,38 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Kel'el</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Porter Jr.</t>
+          <t>Ware</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G141" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -6290,38 +6290,38 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Oso</t>
+          <t>Shai</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Ighodaro</t>
+          <t>Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H147" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J147" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -6330,38 +6330,38 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Luka</t>
+          <t>Jalen</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Doncic</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G148" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H148" t="n">
         <v>11</v>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J148" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -6370,35 +6370,35 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Paolo</t>
+          <t>Bam</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Banchero</t>
+          <t>Adebayo</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="G149" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H149" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J149" t="n">
         <v>1</v>
@@ -6410,38 +6410,38 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Shai</t>
+          <t>Herbert</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Gilgeous-Alexander</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="G150" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H150" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="151">
@@ -6490,38 +6490,38 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Herbert</t>
+          <t>Oso</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Ighodaro</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G152" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I152" t="n">
         <v>1</v>
       </c>
       <c r="J152" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153">
@@ -6530,35 +6530,35 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Bam</t>
+          <t>Paolo</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Adebayo</t>
+          <t>Banchero</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="G153" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H153" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I153" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
         <v>1</v>
@@ -6570,38 +6570,38 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Jalen</t>
+          <t>Luka</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Doncic</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G154" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H154" t="n">
         <v>11</v>
       </c>
       <c r="I154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155">
@@ -6890,38 +6890,38 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Cade</t>
+          <t>Jusuf</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Cunningham</t>
+          <t>Nurkic</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G162" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H162" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -6930,38 +6930,38 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Jusuf</t>
+          <t>Cade</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Nurkic</t>
+          <t>Cunningham</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G163" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H163" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Russell</t>
+          <t>Zach</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Westbrook</t>
+          <t>LaVine</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -7189,19 +7189,19 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="G169" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H169" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I169" t="n">
         <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Zach</t>
+          <t>Russell</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>LaVine</t>
+          <t>Westbrook</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -7229,19 +7229,19 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="G170" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H170" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I170" t="n">
         <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="171">
@@ -7490,38 +7490,38 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Nikola</t>
+          <t>Alperen</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Jokic</t>
+          <t>Sengun</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G177" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H177" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I177" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178">
@@ -7530,38 +7530,38 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Alperen</t>
+          <t>Nikola</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Sengun</t>
+          <t>Jokic</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G178" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H178" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I178" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
@@ -7810,38 +7810,38 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Tre</t>
+          <t>Russell</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Westbrook</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F185" t="n">
         <v>16</v>
       </c>
       <c r="G185" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H185" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J185" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="186">
@@ -7850,38 +7850,38 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Russell</t>
+          <t>Tre</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Westbrook</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F186" t="n">
         <v>16</v>
       </c>
       <c r="G186" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H186" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J186" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187">
@@ -8130,38 +8130,38 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Andre</t>
+          <t>Scottie</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Drummond</t>
+          <t>Barnes</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G193" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H193" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="I193" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194">
@@ -8170,38 +8170,38 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Scottie</t>
+          <t>Andre</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Barnes</t>
+          <t>Drummond</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G194" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H194" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="I194" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -8250,38 +8250,38 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Edwards</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G196" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H196" t="n">
         <v>5</v>
       </c>
       <c r="I196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J196" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -8330,38 +8330,38 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Edwards</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G198" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H198" t="n">
         <v>5</v>
       </c>
       <c r="I198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J198" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="199">
@@ -8370,38 +8370,38 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Tyrese</t>
+          <t>Jalen</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Maxey</t>
+          <t>Suggs</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="G199" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H199" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I199" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J199" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200">
@@ -8410,38 +8410,38 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Jalen</t>
+          <t>Tyrese</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Suggs</t>
+          <t>Maxey</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="G200" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H200" t="n">
+        <v>5</v>
+      </c>
+      <c r="I200" t="n">
         <v>3</v>
       </c>
-      <c r="I200" t="n">
-        <v>2</v>
-      </c>
       <c r="J200" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="201">
@@ -9050,38 +9050,38 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Nikola</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Jokic</t>
+          <t>Reed</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F216" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="G216" t="n">
         <v>6</v>
       </c>
       <c r="H216" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I216" t="n">
         <v>1</v>
       </c>
       <c r="J216" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="217">
@@ -9090,38 +9090,38 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Nikola</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Reed</t>
+          <t>Jokic</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F217" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="G217" t="n">
         <v>6</v>
       </c>
       <c r="H217" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I217" t="n">
         <v>1</v>
       </c>
       <c r="J217" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
@@ -9250,38 +9250,38 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Marcus</t>
+          <t>Cade</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Smart</t>
+          <t>Cunningham</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F221" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="G221" t="n">
+        <v>11</v>
+      </c>
+      <c r="H221" t="n">
+        <v>12</v>
+      </c>
+      <c r="I221" t="n">
+        <v>2</v>
+      </c>
+      <c r="J221" t="n">
         <v>5</v>
-      </c>
-      <c r="H221" t="n">
-        <v>4</v>
-      </c>
-      <c r="I221" t="n">
-        <v>0</v>
-      </c>
-      <c r="J221" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="222">
@@ -9290,38 +9290,38 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Cade</t>
+          <t>Marcus</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Cunningham</t>
+          <t>Smart</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="F222" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="G222" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H222" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I222" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J222" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="223">
@@ -10210,38 +10210,38 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Jay</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Reaves</t>
+          <t>Huff</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F245" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G245" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I245" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J245" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -10290,38 +10290,38 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Jay</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Huff</t>
+          <t>Reaves</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F247" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="G247" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H247" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I247" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J247" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="248">
@@ -10850,38 +10850,38 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Drew</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Eubanks</t>
+          <t>Wembanyama</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F261" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="G261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H261" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I261" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J261" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262">
@@ -10890,38 +10890,38 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>Drew</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Wembanyama</t>
+          <t>Eubanks</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F262" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="G262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H262" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I262" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="263">

--- a/uniqorn-frontend/public/data/CurrentSeason_UniqornGames_Master.xlsx
+++ b/uniqorn-frontend/public/data/CurrentSeason_UniqornGames_Master.xlsx
@@ -486,162 +486,162 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alperen</t>
+          <t>Julian</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sengun</t>
+          <t>Champagnie</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
         <v>3</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bub</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Carrington</t>
+          <t>Williams III</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jaden</t>
+          <t>Dyson</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>McDaniels</t>
+          <t>Daniels</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
         <v>5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rudy</t>
+          <t>Alperen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Gobert</t>
+          <t>Sengun</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -650,38 +650,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Jaden</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>McDaniels</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -726,39 +726,39 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>Rudy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wembanyama</t>
+          <t>Gobert</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
         <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -766,73 +766,73 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46075</v>
+        <v>46077</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Bub</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ingram</t>
+          <t>Carrington</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
         <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46075</v>
+        <v>46077</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Horford</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -841,321 +841,321 @@
         <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46075</v>
+        <v>46076</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nikola</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jokic</t>
+          <t>Wembanyama</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G11" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46074</v>
+        <v>46075</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Matas</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Buzelis</t>
+          <t>Horford</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
         <v>3</v>
-      </c>
-      <c r="H12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46074</v>
+        <v>46075</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tyrese</t>
+          <t>Nikola</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Maxey</t>
+          <t>Jokic</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
         <v>3</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46074</v>
+        <v>46075</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cade</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cunningham</t>
+          <t>Ingram</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Isaiah</t>
+          <t>Matas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Collier</t>
+          <t>Buzelis</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Cade</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rollins</t>
+          <t>Cunningham</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kam</t>
+          <t>Tyrese</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Maxey</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="G17" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>5</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Precious</t>
+          <t>Isaiah</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Achiuwa</t>
+          <t>Collier</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H18" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
         <v>2</v>
@@ -1166,82 +1166,82 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jaylen</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Rollins</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H19" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Derrick</t>
+          <t>Kam</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H20" t="n">
         <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1250,123 +1250,123 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cade</t>
+          <t>Precious</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cunningham</t>
+          <t>Achiuwa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="G21" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I21" t="n">
         <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46065</v>
+        <v>46072</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bobby</t>
+          <t>Jaylen</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portis</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="F22" t="n">
+        <v>23</v>
+      </c>
+      <c r="G22" t="n">
+        <v>13</v>
+      </c>
+      <c r="H22" t="n">
         <v>15</v>
       </c>
-      <c r="G22" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" t="n">
-        <v>12</v>
-      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46065</v>
+        <v>46072</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Donovan</t>
+          <t>Cade</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Clingan</t>
+          <t>Cunningham</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H23" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46064</v>
+        <v>46072</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1385,220 +1385,220 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jalen</t>
+          <t>Donovan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Suggs</t>
+          <t>Clingan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I25" t="n">
         <v>3</v>
       </c>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Josh</t>
+          <t>Bobby</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hart</t>
+          <t>Portis</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>15</v>
       </c>
       <c r="G26" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jalen</t>
+          <t>Derrick</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Suggs</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Maxime</t>
+          <t>Jalen</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Raynaud</t>
+          <t>Suggs</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H28" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Donovan</t>
+          <t>Josh</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mitchell</t>
+          <t>Hart</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>2</v>
@@ -1606,202 +1606,202 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Scottie</t>
+          <t>Maxime</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Barnes</t>
+          <t>Raynaud</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G30" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kawhi</t>
+          <t>Donovan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Leonard</t>
+          <t>Mitchell</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H31" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46060</v>
+        <v>46062</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Jahmai</t>
+          <t>Jalen</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mashack</t>
+          <t>Suggs</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jusuf</t>
+          <t>Kawhi</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nurkic</t>
+          <t>Leonard</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G33" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Alperen</t>
+          <t>Scottie</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sengun</t>
+          <t>Barnes</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G34" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H34" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -1810,38 +1810,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jalen</t>
+          <t>Alperen</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Suggs</t>
+          <t>Sengun</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="F35" t="n">
+        <v>17</v>
+      </c>
+      <c r="G35" t="n">
+        <v>11</v>
+      </c>
+      <c r="H35" t="n">
         <v>12</v>
       </c>
-      <c r="G35" t="n">
-        <v>6</v>
-      </c>
-      <c r="H35" t="n">
-        <v>7</v>
-      </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1850,35 +1850,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nikola</t>
+          <t>Jusuf</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jokic</t>
+          <t>Nurkic</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H36" t="n">
         <v>14</v>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -1886,162 +1886,162 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Derrick</t>
+          <t>Jalen</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Suggs</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46058</v>
+        <v>46060</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Jahmai</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Durant</t>
+          <t>Mashack</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46058</v>
+        <v>46060</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jalen</t>
+          <t>Nikola</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Suggs</t>
+          <t>Jokic</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G39" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H39" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I39" t="n">
         <v>4</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jalen</t>
+          <t>Derrick</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G40" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H40" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2090,118 +2090,118 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Jalen</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kalkbrenner</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H42" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I42" t="n">
         <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Donovan</t>
+          <t>Jalen</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mitchell</t>
+          <t>Suggs</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jalen</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brunson</t>
+          <t>Durant</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NYK</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G44" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -2210,35 +2210,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Neemias</t>
+          <t>Jalen</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Queta</t>
+          <t>Brunson</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NYK</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H45" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>2</v>
@@ -2250,78 +2250,78 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Neemias</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Porter Jr.</t>
+          <t>Queta</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G46" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Filipowski</t>
+          <t>Porter Jr.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G47" t="n">
+        <v>9</v>
+      </c>
+      <c r="H47" t="n">
+        <v>6</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
         <v>5</v>
-      </c>
-      <c r="H47" t="n">
-        <v>16</v>
-      </c>
-      <c r="I47" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -2330,38 +2330,38 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Matas</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Buzelis</t>
+          <t>Filipowski</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -2370,38 +2370,38 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Isaiah</t>
+          <t>Matas</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Collier</t>
+          <t>Buzelis</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G49" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" t="n">
         <v>5</v>
       </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -2410,112 +2410,112 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Jamal</t>
+          <t>Isaiah</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>Collier</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G50" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dominick</t>
+          <t>Jamal</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Barlow</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H51" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Shai</t>
+          <t>Dominick</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Gilgeous-Alexander</t>
+          <t>Barlow</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G52" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H52" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I52" t="n">
         <v>1</v>
@@ -2530,35 +2530,35 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Jarrett</t>
+          <t>Shai</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Allen</t>
+          <t>Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G53" t="n">
+        <v>13</v>
+      </c>
+      <c r="H53" t="n">
         <v>5</v>
       </c>
-      <c r="H53" t="n">
-        <v>17</v>
-      </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>2</v>
@@ -2570,12 +2570,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Craig</t>
+          <t>Jarrett</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Porter Jr.</t>
+          <t>Allen</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2589,19 +2589,19 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="G54" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H54" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -2610,38 +2610,38 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Donovan</t>
+          <t>Craig</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Clingan</t>
+          <t>Porter Jr.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>Cavaliers</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>Trail Blazers</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Cavaliers</t>
-        </is>
-      </c>
       <c r="F55" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G55" t="n">
+        <v>12</v>
+      </c>
+      <c r="H55" t="n">
+        <v>4</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2</v>
+      </c>
+      <c r="J55" t="n">
         <v>5</v>
-      </c>
-      <c r="H55" t="n">
-        <v>12</v>
-      </c>
-      <c r="I55" t="n">
-        <v>4</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2650,78 +2650,78 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cade</t>
+          <t>Donovan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cunningham</t>
+          <t>Clingan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G56" t="n">
+        <v>5</v>
+      </c>
+      <c r="H56" t="n">
         <v>12</v>
       </c>
-      <c r="H56" t="n">
-        <v>4</v>
-      </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Rudy</t>
+          <t>Cade</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Gobert</t>
+          <t>Cunningham</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H57" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
@@ -2730,78 +2730,78 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Yves</t>
+          <t>Rudy</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Missi</t>
+          <t>Gobert</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ausar</t>
+          <t>Yves</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Thompson</t>
+          <t>Missi</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>7</v>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H59" t="n">
         <v>8</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J59" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2886,79 +2886,79 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Myles</t>
+          <t>Ausar</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>Thompson</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H62" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
         <v>6</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Karl-Anthony</t>
+          <t>Myles</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Towns</t>
+          <t>Turner</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3206,42 +3206,42 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Karl-Anthony</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Harden</t>
+          <t>Towns</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G70" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H70" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -3730,38 +3730,38 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cade</t>
+          <t>Jalen</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cunningham</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="F83" t="n">
+        <v>28</v>
+      </c>
+      <c r="G83" t="n">
+        <v>6</v>
+      </c>
+      <c r="H83" t="n">
         <v>16</v>
       </c>
-      <c r="G83" t="n">
-        <v>14</v>
-      </c>
-      <c r="H83" t="n">
-        <v>3</v>
-      </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -3810,38 +3810,38 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Jalen</t>
+          <t>Cade</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Cunningham</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G85" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H85" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -4010,38 +4010,38 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Oso</t>
+          <t>Jaren</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ighodaro</t>
+          <t>Jackson Jr.</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
         <v>3</v>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -4050,38 +4050,38 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Jaren</t>
+          <t>Oso</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jackson Jr.</t>
+          <t>Ighodaro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
         <v>3</v>
       </c>
       <c r="I91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
@@ -4130,38 +4130,38 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Mouhamed</t>
+          <t>Shai</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Gueye</t>
+          <t>Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F93" t="n">
+        <v>34</v>
+      </c>
+      <c r="G93" t="n">
         <v>5</v>
       </c>
-      <c r="G93" t="n">
-        <v>1</v>
-      </c>
       <c r="H93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J93" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -4170,38 +4170,38 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Shai</t>
+          <t>Mouhamed</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Gilgeous-Alexander</t>
+          <t>Gueye</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>4</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
         <v>5</v>
-      </c>
-      <c r="H94" t="n">
-        <v>5</v>
-      </c>
-      <c r="I94" t="n">
-        <v>4</v>
-      </c>
-      <c r="J94" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Kawhi</t>
+          <t>Kris</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Leonard</t>
+          <t>Dunn</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4269,13 +4269,13 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H96" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
@@ -4290,12 +4290,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Kris</t>
+          <t>Kawhi</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dunn</t>
+          <t>Leonard</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4309,13 +4309,13 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="G97" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I97" t="n">
         <v>0</v>
@@ -4410,35 +4410,35 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>Steven</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wembanyama</t>
+          <t>Adams</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G100" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H100" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I100" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J100" t="n">
         <v>2</v>
@@ -4450,38 +4450,38 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Mouhamed</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Gueye</t>
+          <t>Wembanyama</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G101" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H101" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J101" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -4490,38 +4490,38 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Daniss</t>
+          <t>Mouhamed</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jenkins</t>
+          <t>Gueye</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G102" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H102" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
@@ -4530,38 +4530,38 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Steven</t>
+          <t>Daniss</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Adams</t>
+          <t>Jenkins</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G103" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H103" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -4810,38 +4810,38 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Dyson</t>
+          <t>Sandro</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Daniels</t>
+          <t>Mamukelashvili</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
+          <t>Raptors</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
           <t>Hawks</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Raptors</t>
-        </is>
-      </c>
       <c r="F110" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G110" t="n">
+        <v>8</v>
+      </c>
+      <c r="H110" t="n">
         <v>12</v>
       </c>
-      <c r="H110" t="n">
-        <v>5</v>
-      </c>
       <c r="I110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -4850,38 +4850,38 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Dyson</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Kornet</t>
+          <t>Daniels</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G111" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H111" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I111" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -4890,38 +4890,38 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>VJ</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Edgecombe</t>
+          <t>Kornet</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G112" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H112" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I112" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -4930,38 +4930,38 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Sandro</t>
+          <t>VJ</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Mamukelashvili</t>
+          <t>Edgecombe</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Knicks</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G113" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H113" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
@@ -5130,35 +5130,35 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Derrick</t>
+          <t>Cedric</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Coward</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G118" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H118" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I118" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -5170,35 +5170,35 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Cedric</t>
+          <t>Derrick</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Coward</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Celtics</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G119" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H119" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -5210,38 +5210,38 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Kawhi</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Sarr</t>
+          <t>Leonard</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="G120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H120" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I120" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J120" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121">
@@ -5250,38 +5250,38 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Kawhi</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Leonard</t>
+          <t>Sarr</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="G121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I121" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J121" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
@@ -5410,38 +5410,38 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Porter Jr.</t>
+          <t>Wembanyama</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Bucks</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="G125" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H125" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J125" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -5450,38 +5450,38 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Nikola</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Jokic</t>
+          <t>Porter Jr.</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Bucks</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="G126" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H126" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127">
@@ -5530,38 +5530,38 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>Nikola</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Wembanyama</t>
+          <t>Jokic</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G128" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H128" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I128" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -5570,35 +5570,35 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Rudy</t>
+          <t>Nikola</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Gobert</t>
+          <t>Jokic</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
+          <t>Nuggets</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
           <t>Timberwolves</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Nuggets</t>
-        </is>
-      </c>
       <c r="F129" t="n">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H129" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I129" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -5610,35 +5610,35 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Nikola</t>
+          <t>Rudy</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Jokic</t>
+          <t>Gobert</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
+          <t>Timberwolves</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
           <t>Nuggets</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Timberwolves</t>
-        </is>
-      </c>
       <c r="F130" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="G130" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I130" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -5650,38 +5650,38 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Desmond</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bane</t>
+          <t>Harper</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G131" t="n">
+        <v>10</v>
+      </c>
+      <c r="H131" t="n">
+        <v>3</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
         <v>5</v>
-      </c>
-      <c r="H131" t="n">
-        <v>4</v>
-      </c>
-      <c r="I131" t="n">
-        <v>3</v>
-      </c>
-      <c r="J131" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -5690,38 +5690,38 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Nikola</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Harper</t>
+          <t>Jokic</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="G132" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H132" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I132" t="n">
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133">
@@ -5770,38 +5770,38 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Nikola</t>
+          <t>Desmond</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Jokic</t>
+          <t>Bane</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G134" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H134" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I134" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J134" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -5850,38 +5850,38 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Isaiah</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Collier</t>
+          <t>Davis</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="G136" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H136" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -5930,38 +5930,38 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Moussa</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Davis</t>
+          <t>Diabate</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G138" t="n">
         <v>2</v>
       </c>
       <c r="H138" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139">
@@ -5970,38 +5970,38 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Moussa</t>
+          <t>Isaiah</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Diabate</t>
+          <t>Collier</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G139" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H139" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I139" t="n">
         <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
@@ -6090,35 +6090,35 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ausar</t>
+          <t>Reed</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Thompson</t>
+          <t>Sheppard</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="G142" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H142" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I142" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J142" t="n">
         <v>3</v>
@@ -6130,38 +6130,38 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>LaMelo</t>
+          <t>Ausar</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Ball</t>
+          <t>Thompson</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
+          <t>Pistons</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
           <t>Hornets</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Pistons</t>
-        </is>
-      </c>
       <c r="F143" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G143" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H143" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I143" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
@@ -6170,38 +6170,38 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Reed</t>
+          <t>LaMelo</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Sheppard</t>
+          <t>Ball</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="G144" t="n">
         <v>6</v>
       </c>
       <c r="H144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I144" t="n">
         <v>2</v>
       </c>
       <c r="J144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -6290,38 +6290,38 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Shai</t>
+          <t>LaMelo</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Gilgeous-Alexander</t>
+          <t>Ball</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G147" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H147" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -6490,38 +6490,38 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Oso</t>
+          <t>Shai</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Ighodaro</t>
+          <t>Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Thunder</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H152" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J152" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153">
@@ -6610,38 +6610,38 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Keegan</t>
+          <t>Oso</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>Ighodaro</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Warriors</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G155" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I155" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J155" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156">
@@ -6650,38 +6650,38 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>LaMelo</t>
+          <t>Keegan</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Ball</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G156" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H156" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -6730,38 +6730,38 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Jaren</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Durant</t>
+          <t>Jackson Jr.</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G158" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H158" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I158" t="n">
         <v>5</v>
       </c>
       <c r="J158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
@@ -6770,38 +6770,38 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Jaren</t>
+          <t>Lauri</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Jackson Jr.</t>
+          <t>Markkanen</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G159" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H159" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I159" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J159" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160">
@@ -6810,38 +6810,38 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Lauri</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Markkanen</t>
+          <t>Durant</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G160" t="n">
+        <v>7</v>
+      </c>
+      <c r="H160" t="n">
         <v>5</v>
       </c>
-      <c r="H160" t="n">
-        <v>16</v>
-      </c>
       <c r="I160" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J160" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -7130,38 +7130,38 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Nic</t>
+          <t>Zach</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Claxton</t>
+          <t>LaVine</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="G168" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H168" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I168" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Zach</t>
+          <t>Russell</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>LaVine</t>
+          <t>Westbrook</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -7189,19 +7189,19 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="G169" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H169" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I169" t="n">
         <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170">
@@ -7210,38 +7210,38 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Russell</t>
+          <t>Nic</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Westbrook</t>
+          <t>Claxton</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G170" t="n">
         <v>10</v>
       </c>
       <c r="H170" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I170" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J170" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -7490,38 +7490,38 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Alperen</t>
+          <t>Goga</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Sengun</t>
+          <t>Bitadze</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="G177" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H177" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I177" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178">
@@ -7570,38 +7570,38 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Goga</t>
+          <t>Alperen</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Bitadze</t>
+          <t>Sengun</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F179" t="n">
+        <v>31</v>
+      </c>
+      <c r="G179" t="n">
+        <v>14</v>
+      </c>
+      <c r="H179" t="n">
         <v>8</v>
       </c>
-      <c r="G179" t="n">
-        <v>3</v>
-      </c>
-      <c r="H179" t="n">
+      <c r="I179" t="n">
         <v>5</v>
       </c>
-      <c r="I179" t="n">
-        <v>4</v>
-      </c>
       <c r="J179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -7810,38 +7810,38 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Russell</t>
+          <t>Tre</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Westbrook</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F185" t="n">
         <v>16</v>
       </c>
       <c r="G185" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H185" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J185" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186">
@@ -7850,38 +7850,38 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Tre</t>
+          <t>Zach</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Edey</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G186" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H186" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I186" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J186" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -7890,38 +7890,38 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Zach</t>
+          <t>Russell</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Edey</t>
+          <t>Westbrook</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G187" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H187" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I187" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J187" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="188">
@@ -8010,32 +8010,32 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Jalen</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Suggs</t>
+          <t>Sarr</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="n">
         <v>11</v>
-      </c>
-      <c r="H190" t="n">
-        <v>5</v>
       </c>
       <c r="I190" t="n">
         <v>2</v>
@@ -8050,32 +8050,32 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Jalen</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Sarr</t>
+          <t>Suggs</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="G191" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H191" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I191" t="n">
         <v>2</v>
@@ -8250,38 +8250,38 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Jalen</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F196" t="n">
+        <v>14</v>
+      </c>
+      <c r="G196" t="n">
+        <v>2</v>
+      </c>
+      <c r="H196" t="n">
+        <v>2</v>
+      </c>
+      <c r="I196" t="n">
         <v>5</v>
       </c>
-      <c r="G196" t="n">
-        <v>12</v>
-      </c>
-      <c r="H196" t="n">
-        <v>5</v>
-      </c>
-      <c r="I196" t="n">
-        <v>2</v>
-      </c>
       <c r="J196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -8290,38 +8290,38 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Jalen</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Edwards</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="G197" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H197" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I197" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J197" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="198">
@@ -8330,38 +8330,38 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Edwards</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G198" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H198" t="n">
         <v>5</v>
       </c>
       <c r="I198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J198" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -8530,38 +8530,38 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Lauri</t>
+          <t>Alperen</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Markkanen</t>
+          <t>Sengun</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G203" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H203" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I203" t="n">
         <v>2</v>
       </c>
       <c r="J203" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -8570,38 +8570,38 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Jusuf</t>
+          <t>Josh</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Nurkic</t>
+          <t>Giddey</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
+          <t>Bulls</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
           <t>Jazz</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>Bulls</t>
-        </is>
-      </c>
       <c r="F204" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="G204" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H204" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
@@ -8610,38 +8610,38 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Josh</t>
+          <t>Keyonte</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Giddey</t>
+          <t>George</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
+          <t>Jazz</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
           <t>Bulls</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>Jazz</t>
-        </is>
-      </c>
       <c r="F205" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G205" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H205" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J205" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="206">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Keyonte</t>
+          <t>Lauri</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>Markkanen</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -8669,19 +8669,19 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="G206" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H206" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I206" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J206" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207">
@@ -8690,38 +8690,38 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Alperen</t>
+          <t>Jusuf</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Sengun</t>
+          <t>Nurkic</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G207" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H207" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J207" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="208">
@@ -8970,38 +8970,38 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Jalen</t>
+          <t>Scottie</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Barnes</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Cavaliers</t>
         </is>
       </c>
       <c r="F214" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G214" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H214" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I214" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J214" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
@@ -9010,38 +9010,38 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Scottie</t>
+          <t>Jalen</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Barnes</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F215" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G215" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H215" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I215" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J215" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="216">
@@ -9050,38 +9050,38 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Nikola</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Reed</t>
+          <t>Jokic</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F216" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="G216" t="n">
         <v>6</v>
       </c>
       <c r="H216" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I216" t="n">
         <v>1</v>
       </c>
       <c r="J216" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
@@ -9090,38 +9090,38 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Nikola</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Jokic</t>
+          <t>Reed</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F217" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="G217" t="n">
         <v>6</v>
       </c>
       <c r="H217" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I217" t="n">
         <v>1</v>
       </c>
       <c r="J217" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="218">
@@ -9210,38 +9210,38 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>Cade</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Wembanyama</t>
+          <t>Cunningham</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Bulls</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F220" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G220" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H220" t="n">
         <v>12</v>
       </c>
       <c r="I220" t="n">
+        <v>2</v>
+      </c>
+      <c r="J220" t="n">
         <v>5</v>
-      </c>
-      <c r="J220" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -9250,38 +9250,38 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Cade</t>
+          <t>Marcus</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Cunningham</t>
+          <t>Smart</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F221" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="G221" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H221" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I221" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J221" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="222">
@@ -9290,38 +9290,38 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Marcus</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Smart</t>
+          <t>Wembanyama</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>Bulls</t>
         </is>
       </c>
       <c r="F222" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="G222" t="n">
         <v>5</v>
       </c>
       <c r="H222" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I222" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J222" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
@@ -9340,19 +9340,19 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="F223" t="n">
         <v>13</v>
       </c>
       <c r="G223" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H223" t="n">
         <v>4</v>
@@ -9610,38 +9610,38 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Jalen</t>
+          <t>Alperen</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Duren</t>
+          <t>Sengun</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F230" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G230" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H230" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I230" t="n">
         <v>1</v>
       </c>
       <c r="J230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
@@ -9690,38 +9690,38 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Alperen</t>
+          <t>Jalen</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Sengun</t>
+          <t>Duren</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Pistons</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F232" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G232" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H232" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I232" t="n">
         <v>1</v>
       </c>
       <c r="J232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -10010,38 +10010,38 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Kalkbrenner</t>
+          <t>Booker</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="F240" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="G240" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H240" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I240" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J240" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
@@ -10050,38 +10050,38 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Devin</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Booker</t>
+          <t>Kalkbrenner</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F241" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G241" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H241" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I241" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J241" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="242">
@@ -10210,38 +10210,38 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Jay</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Huff</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F245" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G245" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H245" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I245" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J245" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="246">
@@ -10250,38 +10250,38 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Reaves</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="F246" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G246" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H246" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J246" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="247">
@@ -10290,38 +10290,38 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Jay</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Reaves</t>
+          <t>Huff</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F247" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G247" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H247" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I247" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J247" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -10850,38 +10850,38 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>Drew</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Wembanyama</t>
+          <t>Eubanks</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Suns</t>
         </is>
       </c>
       <c r="F261" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="G261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H261" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I261" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="262">
@@ -10890,38 +10890,38 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Drew</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Eubanks</t>
+          <t>Wembanyama</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="F262" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="G262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H262" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I262" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
